--- a/YRIGOYEN 9730/Julio/YRIGOYEN9730-Julio.xlsx
+++ b/YRIGOYEN 9730/Julio/YRIGOYEN9730-Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9730\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ECBA71-F2B4-4454-A2BF-51FE3ED538E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F9ECF8-6BB8-42B3-8DD2-089F957D87A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$130</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="122">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -320,48 +320,24 @@
     <t>SALDO EN BANCO</t>
   </si>
   <si>
-    <t>VTO 14/07</t>
-  </si>
-  <si>
-    <t>PERÍODO: JUNIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JUNIO</t>
-  </si>
-  <si>
     <t>Romanatti carlos - Certificacion copias digitales</t>
   </si>
   <si>
-    <t>Ascensores lema - Mantenimiento mayo</t>
-  </si>
-  <si>
-    <t>Ascensores lema - Mantenimiento abril</t>
-  </si>
-  <si>
     <t>Debito 09/06</t>
   </si>
   <si>
     <t>Mes anterior</t>
   </si>
   <si>
-    <t>Sindicatos mes de MAYO</t>
-  </si>
-  <si>
     <t>Debito 12/06</t>
   </si>
   <si>
-    <t>Debito 13/06</t>
-  </si>
-  <si>
     <t>Debito 17/06</t>
   </si>
   <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>GUSTAVO PADRON - SR CONTADOR - ABRIL Y MAYO</t>
-  </si>
-  <si>
     <t>Transf 12/06</t>
   </si>
   <si>
@@ -371,25 +347,52 @@
     <t>Efectivo 09/06</t>
   </si>
   <si>
-    <t>Incluye SAC</t>
-  </si>
-  <si>
-    <t>Adelanto arreglo Julio Doartero - Cambio de caño cloacal UF 14</t>
-  </si>
-  <si>
-    <t>Transf 30/06</t>
-  </si>
-  <si>
     <t>Ingeso ya identificado de UF 7 Abril</t>
   </si>
   <si>
-    <t>Ingreso ya identificado de UF 7 Mayo</t>
-  </si>
-  <si>
     <t>laurasmiet@gmail.com</t>
   </si>
   <si>
     <t>AGREGAR A LA CADENA</t>
+  </si>
+  <si>
+    <t>VTO 14/08</t>
+  </si>
+  <si>
+    <t>PERÍODO: JULIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JULIO</t>
+  </si>
+  <si>
+    <t>GUSTAVO PADRON - SR CONTADOR - ABRIL Y junio</t>
+  </si>
+  <si>
+    <t>Ascensores lema - Mantenimiento junio</t>
+  </si>
+  <si>
+    <t>Ingreso ya identificado de UF 7 junio</t>
+  </si>
+  <si>
+    <t>Incluye</t>
+  </si>
+  <si>
+    <t>Transf 17/7</t>
+  </si>
+  <si>
+    <t>Matafuegos</t>
+  </si>
+  <si>
+    <t>Transf 14/07</t>
+  </si>
+  <si>
+    <t>Transf 10/07</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Cambio de caño cloacal UF 14</t>
+  </si>
+  <si>
+    <t>Debito 14/07</t>
   </si>
 </sst>
 </file>
@@ -397,14 +400,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1103,11 +1106,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1115,7 +1118,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1130,9 +1133,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1147,7 +1150,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1157,40 +1160,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1204,7 +1207,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1212,99 +1215,99 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1313,73 +1316,79 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1411,10 +1420,19 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1432,12 +1450,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,16 +1465,12 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1828,22 +1836,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M136"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M134"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>60</v>
@@ -1852,7 +1860,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>29</v>
@@ -1861,16 +1869,16 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="200"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1881,12 +1889,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1894,7 +1902,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>61</v>
       </c>
@@ -1905,57 +1913,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="202" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="202"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="202"/>
-      <c r="C10" s="202"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="204" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="204"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="201"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="201"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="203"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="203"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1964,7 +1972,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>36</v>
       </c>
@@ -1973,12 +1981,12 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="163">
@@ -1986,21 +1994,21 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="163"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="163"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
@@ -2011,20 +2019,20 @@
       </c>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
-      <c r="D26" s="174">
+      <c r="D26" s="173">
         <f>SUM(D22:D25)</f>
         <v>1074415</v>
       </c>
       <c r="E26" s="146"/>
       <c r="G26" s="22"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
@@ -2033,1002 +2041,965 @@
       <c r="D27" s="163"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="163"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="163"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="175"/>
+      <c r="D30" s="174"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="175"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="175"/>
+      <c r="D32" s="174"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="175">
+      <c r="D33" s="174">
         <v>0</v>
       </c>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="175"/>
+      <c r="D34" s="174"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="59" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="59"/>
       <c r="C35" s="59"/>
-      <c r="D35" s="176">
+      <c r="D35" s="175">
         <f>SUM(D27:D34)</f>
         <v>0</v>
       </c>
       <c r="E35" s="146"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
-      <c r="D36" s="177"/>
+      <c r="D36" s="176"/>
       <c r="E36" s="147">
         <f>D26+D35</f>
         <v>1074415</v>
       </c>
       <c r="F36" s="22"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
-      <c r="D37" s="178"/>
+      <c r="D37" s="177"/>
       <c r="E37" s="148"/>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="195" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" s="196"/>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="198"/>
       <c r="C38" s="54"/>
-      <c r="D38" s="163">
-        <f>2*28000</f>
-        <v>56000</v>
+      <c r="D38" s="222">
+        <f>2*30000</f>
+        <v>60000</v>
       </c>
       <c r="E38" s="149"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="195" t="s">
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="197" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="196"/>
+      <c r="B39" s="198"/>
       <c r="C39" s="54"/>
-      <c r="D39" s="179">
+      <c r="D39" s="178">
         <v>107000</v>
       </c>
       <c r="E39" s="149"/>
       <c r="H39" s="161"/>
     </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
-      <c r="D40" s="180"/>
+      <c r="D40" s="179"/>
       <c r="E40" s="150">
         <f>SUM(D38:D39)</f>
-        <v>163000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>167000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
-      <c r="D41" s="181"/>
+      <c r="D41" s="180"/>
       <c r="E41" s="151"/>
     </row>
-    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="193" t="s">
+    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="194"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="56"/>
-      <c r="D42" s="182">
+      <c r="D42" s="181">
         <v>71883</v>
       </c>
       <c r="E42" s="152"/>
     </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="193" t="s">
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="195" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="194"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="56"/>
-      <c r="D43" s="183">
+      <c r="D43" s="182">
         <v>131172</v>
       </c>
       <c r="E43" s="152"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
-      <c r="D44" s="180"/>
+      <c r="D44" s="179"/>
       <c r="E44" s="153">
         <f>SUM(D42:D43)</f>
         <v>203055</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B45" s="154"/>
       <c r="C45" s="154"/>
-      <c r="D45" s="184"/>
+      <c r="D45" s="183"/>
       <c r="E45" s="155"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="185">
-        <v>516520.58</v>
+      <c r="D46" s="223">
+        <v>781413.99</v>
       </c>
       <c r="E46" s="164" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G46" s="128"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C47" s="54"/>
-      <c r="D47" s="185">
-        <v>516572.55</v>
-      </c>
+      <c r="D47" s="184"/>
       <c r="E47" s="164" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G47" s="128"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="185">
+      <c r="D48" s="184">
         <v>10602.27</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="185">
+      <c r="D49" s="184">
         <v>75532.289999999994</v>
       </c>
       <c r="E49" s="164" t="str">
         <f>E48</f>
         <v>Debito 17/06</v>
       </c>
-      <c r="G49" s="144">
-        <f>D49+D48</f>
-        <v>86134.56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="144"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="185">
-        <v>42392.29</v>
+      <c r="C50" s="5"/>
+      <c r="D50" s="220">
+        <v>111004.57</v>
       </c>
       <c r="E50" s="164" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="185">
-        <v>73233.31</v>
-      </c>
-      <c r="E51" s="164" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C51" s="5"/>
+      <c r="D51" s="220">
+        <v>7138.97</v>
+      </c>
+      <c r="E51" s="165" t="str">
+        <f>E50</f>
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="str">
         <f>A51</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="185">
-        <v>4710.25</v>
-      </c>
-      <c r="E52" s="164" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="167">
-        <v>60556.13</v>
-      </c>
-      <c r="E53" s="164" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="str">
-        <f>A53</f>
-        <v>Sindicatos mes de JUNIO</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="167">
-        <v>3695.7</v>
-      </c>
-      <c r="E54" s="165" t="str">
-        <f>E53</f>
-        <v>Debito 13/06</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="str">
-        <f>A54</f>
-        <v>Sindicatos mes de JUNIO</v>
+      <c r="C52" s="5"/>
+      <c r="D52" s="220">
+        <v>64250.7</v>
+      </c>
+      <c r="E52" s="166" t="str">
+        <f>E51</f>
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="185"/>
+      <c r="E53" s="153">
+        <f>SUM(D46:D52)</f>
+        <v>1049942.79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="154"/>
+      <c r="C54" s="154"/>
+      <c r="D54" s="183"/>
+      <c r="E54" s="155"/>
+    </row>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="167">
-        <v>33261.300000000003</v>
-      </c>
-      <c r="E55" s="166" t="str">
-        <f>E54</f>
-        <v>Debito 13/06</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="154"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="186"/>
-      <c r="E56" s="153">
-        <f>SUM(D46:D55)</f>
-        <v>1337076.67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" s="154"/>
-      <c r="C57" s="154"/>
-      <c r="D57" s="184"/>
-      <c r="E57" s="155"/>
-    </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="5"/>
+      <c r="D55" s="220">
+        <v>52544.74</v>
+      </c>
+      <c r="E55" s="164" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" s="167"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="220">
+        <v>23727.17</v>
+      </c>
+      <c r="E56" s="164" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="167">
+        <v>25728.934000000001</v>
+      </c>
+      <c r="E57" s="164" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="195" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="196"/>
       <c r="C58" s="5"/>
       <c r="D58" s="167">
-        <f>89284.14-35225.95</f>
-        <v>54058.19</v>
+        <v>355815.42</v>
       </c>
       <c r="E58" s="164" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B59" s="167"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="167">
-        <f>54218.7-17757.17</f>
-        <v>36461.53</v>
-      </c>
-      <c r="E59" s="164" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="167">
-        <v>25728.934000000001</v>
-      </c>
-      <c r="E60" s="164" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="193" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="194"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="186"/>
+      <c r="E59" s="153">
+        <f>SUM(D55:D58)</f>
+        <v>457816.26399999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="36"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="179"/>
+      <c r="E60" s="157"/>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="201" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" s="202"/>
       <c r="C61" s="5"/>
       <c r="D61" s="167">
-        <v>355815.42</v>
-      </c>
-      <c r="E61" s="164" t="s">
+        <v>229307.1</v>
+      </c>
+      <c r="E61" s="168" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="187"/>
-      <c r="E62" s="153">
-        <f>SUM(D58:D61)</f>
-        <v>472064.07400000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="180"/>
-      <c r="E63" s="157"/>
-    </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="199" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="200"/>
+    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="170" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" s="162"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="167">
+        <v>54500</v>
+      </c>
+      <c r="E62" s="168" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="197" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="198"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="220">
+        <v>129500</v>
+      </c>
+      <c r="E63" s="168" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="188" t="s">
+        <v>102</v>
+      </c>
+      <c r="B64" s="189"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="167">
-        <v>229307.1</v>
-      </c>
-      <c r="E64" s="168" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="171" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" s="162"/>
+      <c r="D64" s="132">
+        <v>59450</v>
+      </c>
+      <c r="E64" s="169" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="188"/>
+      <c r="B65" s="189"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="167">
-        <v>54500</v>
-      </c>
-      <c r="E65" s="168" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="195" t="s">
-        <v>102</v>
-      </c>
-      <c r="B66" s="196"/>
+      <c r="D65" s="132">
+        <v>44480.41</v>
+      </c>
+      <c r="E65" s="169"/>
+    </row>
+    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="197" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" s="198"/>
       <c r="C66" s="5"/>
-      <c r="D66" s="167">
-        <v>54500</v>
-      </c>
-      <c r="E66" s="168" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="189" t="s">
-        <v>109</v>
-      </c>
-      <c r="B67" s="190"/>
+      <c r="D66" s="132">
+        <v>35000</v>
+      </c>
+      <c r="E66" s="169" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="195" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="196"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="110">
-        <v>75810</v>
-      </c>
-      <c r="E67" s="169"/>
-    </row>
-    <row r="68" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="195" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="196"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="110">
-        <v>30000</v>
-      </c>
-      <c r="E68" s="168" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="193" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="194"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="110">
-        <v>300000</v>
-      </c>
-      <c r="E69" s="170" t="s">
-        <v>116</v>
-      </c>
-      <c r="I69" s="193"/>
-      <c r="J69" s="194"/>
-    </row>
-    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="30" t="s">
+      <c r="D67" s="132">
+        <v>550000</v>
+      </c>
+      <c r="E67" s="221" t="s">
+        <v>119</v>
+      </c>
+      <c r="I67" s="195"/>
+      <c r="J67" s="196"/>
+    </row>
+    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="158">
-        <f>SUM(D64:D69)</f>
-        <v>744117.1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="36" t="s">
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="158">
+        <f>SUM(D61:D67)</f>
+        <v>1102237.51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B71" s="69"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="177"/>
-      <c r="E71" s="157"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+      <c r="B69" s="69"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="176"/>
+      <c r="E69" s="157"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="167">
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="167">
         <v>33531.78</v>
       </c>
-      <c r="E72" s="159"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E70" s="159"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="156"/>
+      <c r="E71" s="41"/>
+    </row>
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="53"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="107">
+        <f>SUM(D70:D71)</f>
+        <v>33531.78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="156"/>
-      <c r="E73" s="41"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="53"/>
-      <c r="C74" s="53"/>
-      <c r="D74" s="113"/>
-      <c r="E74" s="107">
-        <f>SUM(D72:D73)</f>
-        <v>33531.78</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="106"/>
-      <c r="E75" s="114"/>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="31" t="s">
+      <c r="D73" s="106"/>
+      <c r="E73" s="114"/>
+    </row>
+    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B76" s="31"/>
-      <c r="C76" s="31"/>
-      <c r="D76" s="115"/>
-      <c r="E76" s="116"/>
-    </row>
-    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="115"/>
+      <c r="E74" s="116"/>
+    </row>
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="1"/>
+      <c r="D75" s="117"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="45"/>
+    </row>
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="119"/>
+      <c r="E76" s="120">
+        <f>(SUM(E29:E74))</f>
+        <v>4087998.344</v>
+      </c>
+      <c r="F76" s="144"/>
+      <c r="G76" s="45"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D77" s="117"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="45"/>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="119"/>
-      <c r="E78" s="120">
-        <f>(SUM(E29:E76))</f>
-        <v>4027259.6239999998</v>
-      </c>
-      <c r="F78" s="144"/>
-      <c r="G78" s="45"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D79" s="117"/>
-      <c r="E79" s="117"/>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="117"/>
-      <c r="E80" s="117"/>
-      <c r="H80" s="188"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
+      <c r="E77" s="117"/>
+    </row>
+    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D78" s="117"/>
+      <c r="E78" s="117"/>
+      <c r="H78" s="187"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B81" s="12"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="121"/>
-      <c r="E81" s="122"/>
-    </row>
-    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="193"/>
-      <c r="B82" s="194"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="121"/>
+      <c r="E79" s="122"/>
+    </row>
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="195"/>
+      <c r="B80" s="196"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="132"/>
+      <c r="E80" s="108"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="195"/>
+      <c r="B81" s="196"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="110"/>
+      <c r="E81" s="108"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="197"/>
+      <c r="B82" s="198"/>
       <c r="C82" s="5"/>
-      <c r="D82" s="132"/>
+      <c r="D82" s="110"/>
       <c r="E82" s="108"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="193"/>
-      <c r="B83" s="194"/>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="109"/>
+      <c r="B83" s="111"/>
       <c r="C83" s="5"/>
       <c r="D83" s="110"/>
       <c r="E83" s="108"/>
     </row>
-    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="195"/>
-      <c r="B84" s="196"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="110"/>
-      <c r="E84" s="108"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="109"/>
-      <c r="B85" s="111"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="110"/>
-      <c r="E85" s="108"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="51"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="60"/>
-      <c r="E86" s="60">
-        <f>SUM(D82:D85)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="31" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="51"/>
+      <c r="B84" s="50"/>
+      <c r="C84" s="50"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60">
+        <f>SUM(D80:D83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B89" s="31"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="105"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="105"/>
+    </row>
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B91" s="10"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="70">
-        <f>E86+E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="10"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="70">
+        <f>E84+E87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="104">
+        <f>E76</f>
+        <v>4087998.344</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" s="104">
+        <f>E76-E74</f>
+        <v>4087998.344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="103" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B93" s="104">
-        <f>E78</f>
-        <v>4027259.6239999998</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E89-E87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="103" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B94" s="104">
-        <f>E78-E76</f>
-        <v>4027259.6239999998</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="104">
-        <f>E91-E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="B96" s="104">
-        <f>E91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="203"/>
-      <c r="B99" s="203"/>
-      <c r="C99" s="203"/>
-      <c r="D99" s="203"/>
-      <c r="E99" s="203"/>
-    </row>
-    <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="203"/>
-      <c r="B100" s="203"/>
-      <c r="C100" s="203"/>
-      <c r="D100" s="203"/>
-      <c r="E100" s="203"/>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="203"/>
-      <c r="B101" s="203"/>
-      <c r="C101" s="203"/>
-      <c r="D101" s="203"/>
-      <c r="E101" s="203"/>
-    </row>
-    <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="23" t="s">
+        <f>E89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="193"/>
+      <c r="B97" s="193"/>
+      <c r="C97" s="193"/>
+      <c r="D97" s="193"/>
+      <c r="E97" s="193"/>
+    </row>
+    <row r="98" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="193"/>
+      <c r="B98" s="193"/>
+      <c r="C98" s="193"/>
+      <c r="D98" s="193"/>
+      <c r="E98" s="193"/>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="193"/>
+      <c r="B99" s="193"/>
+      <c r="C99" s="193"/>
+      <c r="D99" s="193"/>
+      <c r="E99" s="193"/>
+    </row>
+    <row r="101" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B103" s="129"/>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="34"/>
-      <c r="B104" s="61">
-        <v>0</v>
-      </c>
-      <c r="C104" s="26"/>
-    </row>
-    <row r="105" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="25" t="s">
+      <c r="B101" s="129"/>
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="34"/>
+      <c r="B102" s="61">
+        <v>0</v>
+      </c>
+      <c r="C102" s="26"/>
+    </row>
+    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="41">
+      <c r="B103" s="41">
         <f>PRORRATEO!F29</f>
         <v>2620698.6400000006</v>
       </c>
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="25"/>
+      <c r="B104" s="41">
+        <v>0</v>
+      </c>
+      <c r="C104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B105" s="112">
+        <f>B129</f>
+        <v>0</v>
+      </c>
       <c r="C105" s="24"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="25"/>
-      <c r="B106" s="41">
-        <v>0</v>
-      </c>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="28"/>
+      <c r="B106" s="49"/>
       <c r="C106" s="24"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B107" s="112">
-        <f>B131</f>
-        <v>0</v>
-      </c>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="B107" s="49"/>
       <c r="C107" s="24"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="28"/>
-      <c r="B108" s="49"/>
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108" s="49">
+        <f>-B92</f>
+        <v>-4087998.344</v>
+      </c>
       <c r="C108" s="24"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="127" t="s">
-        <v>51</v>
-      </c>
-      <c r="B109" s="49"/>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B109" s="49">
+        <f>-(B93)</f>
+        <v>0</v>
+      </c>
       <c r="C109" s="24"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B110" s="49">
-        <f>-B94</f>
-        <v>-4027259.6239999998</v>
-      </c>
-      <c r="C110" s="24"/>
-    </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B111" s="49">
-        <f>-(B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C111" s="24"/>
-    </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="33" t="s">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="61">
-        <f>SUM(B104:B111)</f>
-        <v>-1406560.9839999992</v>
-      </c>
+      <c r="B110" s="61">
+        <f>SUM(B102:B109)</f>
+        <v>-1467299.7039999994</v>
+      </c>
+      <c r="C110" s="27"/>
+      <c r="D110" s="45"/>
+    </row>
+    <row r="111" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B111" s="42"/>
+      <c r="C111" s="27"/>
+      <c r="D111" s="45"/>
+      <c r="E111" s="130"/>
+      <c r="F111" s="131"/>
+    </row>
+    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="43"/>
       <c r="C112" s="27"/>
-      <c r="D112" s="45"/>
-    </row>
-    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:5" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113"/>
       <c r="B113" s="42"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="130"/>
-      <c r="F113" s="131"/>
-    </row>
-    <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="43"/>
-      <c r="C114" s="27"/>
-    </row>
-    <row r="115" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115"/>
-      <c r="B115" s="42"/>
-      <c r="C115" s="38"/>
-    </row>
-    <row r="116" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="135" t="s">
+      <c r="C113" s="38"/>
+    </row>
+    <row r="114" spans="1:5" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B116" s="136">
+      <c r="B114" s="136">
         <v>1598636.2300000009</v>
       </c>
-      <c r="C116" s="38"/>
-      <c r="D116" s="48"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C114" s="38"/>
+      <c r="D114" s="48"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B115" s="141">
+        <f>-B92</f>
+        <v>-4087998.344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B116" s="141">
+        <f>-B93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B117" s="141">
-        <f>-B94</f>
-        <v>-4027259.6239999998</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="B117" s="191">
+        <v>-129805</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B118" s="141">
-        <f>-B95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="B118" s="191">
+        <v>-129843</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="B119" s="192">
-        <v>-129805</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="B119" s="141">
+        <f>B129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="B120" s="192">
-        <v>-129843</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="B121" s="141">
-        <f>B131</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B122" s="142">
+      <c r="B120" s="142">
         <f>PRORRATEO!F29</f>
         <v>2620698.6400000006</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="143" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="B123" s="191">
+      <c r="B121" s="190">
         <f>-7906.2621-11800</f>
         <v>-19706.2621</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="139" t="s">
+    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B124" s="140">
-        <f>SUM(B116:C123)</f>
-        <v>-87279.01609999832</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="137"/>
-      <c r="B125" s="137"/>
-    </row>
-    <row r="126" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="204" t="s">
+      <c r="B122" s="140">
+        <f>SUM(B114:C121)</f>
+        <v>-148017.73609999852</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="137"/>
+      <c r="B123" s="137"/>
+    </row>
+    <row r="124" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="194" t="s">
         <v>34</v>
       </c>
-      <c r="B127" s="204"/>
-      <c r="C127" s="204"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="204"/>
-      <c r="B128" s="204"/>
-      <c r="C128" s="204"/>
-    </row>
-    <row r="129" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="124"/>
-      <c r="B129" s="37"/>
-      <c r="C129" s="37">
+      <c r="B125" s="194"/>
+      <c r="C125" s="194"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="194"/>
+      <c r="B126" s="194"/>
+      <c r="C126" s="194"/>
+    </row>
+    <row r="127" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="124"/>
+      <c r="B127" s="37"/>
+      <c r="C127" s="37">
         <v>40000</v>
       </c>
-      <c r="E129" s="144"/>
-    </row>
-    <row r="130" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="124"/>
-      <c r="B130" s="126"/>
-      <c r="C130" s="123"/>
-      <c r="D130" s="144"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="46" t="s">
+      <c r="E127" s="144"/>
+    </row>
+    <row r="128" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="124"/>
+      <c r="B128" s="126"/>
+      <c r="C128" s="123"/>
+      <c r="D128" s="144"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B131" s="125">
-        <f>SUM(B129:B130)</f>
-        <v>0</v>
-      </c>
-      <c r="C131" s="47"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M132" s="8"/>
-    </row>
-    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="203"/>
-      <c r="B133" s="203"/>
-      <c r="C133" s="203"/>
-      <c r="D133" s="203"/>
-      <c r="E133" s="203"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="203"/>
-      <c r="B134" s="203"/>
-      <c r="C134" s="203"/>
-      <c r="D134" s="203"/>
-      <c r="E134" s="203"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="203"/>
-      <c r="B135" s="203"/>
-      <c r="C135" s="203"/>
-      <c r="D135" s="203"/>
-      <c r="E135" s="203"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="203"/>
-      <c r="B136" s="203"/>
-      <c r="C136" s="203"/>
-      <c r="D136" s="203"/>
-      <c r="E136" s="203"/>
+      <c r="B129" s="125">
+        <f>SUM(B127:B128)</f>
+        <v>0</v>
+      </c>
+      <c r="C129" s="47"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M130" s="8"/>
+    </row>
+    <row r="131" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="193"/>
+      <c r="B131" s="193"/>
+      <c r="C131" s="193"/>
+      <c r="D131" s="193"/>
+      <c r="E131" s="193"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="193"/>
+      <c r="B132" s="193"/>
+      <c r="C132" s="193"/>
+      <c r="D132" s="193"/>
+      <c r="E132" s="193"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="193"/>
+      <c r="B133" s="193"/>
+      <c r="C133" s="193"/>
+      <c r="D133" s="193"/>
+      <c r="E133" s="193"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="193"/>
+      <c r="B134" s="193"/>
+      <c r="C134" s="193"/>
+      <c r="D134" s="193"/>
+      <c r="E134" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A133:E136"/>
-    <mergeCell ref="A127:C128"/>
-    <mergeCell ref="A99:E101"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A131:E134"/>
+    <mergeCell ref="A125:C126"/>
+    <mergeCell ref="A97:E99"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A82:B82"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3039,46 +3010,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="0.109375" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3086,7 +3057,7 @@
         <v>93</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="172">
+      <c r="F2" s="171">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -3104,7 +3075,7 @@
       <c r="O2" s="57"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3121,75 +3092,75 @@
       <c r="N3" s="58"/>
       <c r="O3" s="62"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="210" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="207" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="211" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="210" t="s">
+      <c r="F4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="210" t="s">
+      <c r="G4" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="211" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="211" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="206" t="s">
+      <c r="K4" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>91</v>
       </c>
       <c r="M4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="208" t="s">
+      <c r="N4" s="213" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="217" t="s">
+      <c r="O4" s="205" t="s">
         <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="211"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="207"/>
-      <c r="L5" s="216"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="209"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="219"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/07</v>
-      </c>
-      <c r="N5" s="209"/>
-      <c r="O5" s="218"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 14/08</v>
+      </c>
+      <c r="N5" s="214"/>
+      <c r="O5" s="206"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3223,7 +3194,7 @@
         <f>M$2*D6/100</f>
         <v>187320</v>
       </c>
-      <c r="L6" s="173">
+      <c r="L6" s="172">
         <f>F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
@@ -3243,7 +3214,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3278,7 +3249,7 @@
         <f t="shared" ref="K7:K23" si="2">M$2*D7%</f>
         <v>164640</v>
       </c>
-      <c r="L7" s="173">
+      <c r="L7" s="172">
         <f t="shared" ref="L7:L23" si="3">F$2*D7/100</f>
         <v>5064.7121280000001</v>
       </c>
@@ -3300,7 +3271,7 @@
       </c>
       <c r="Q7" s="45"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3334,7 +3305,7 @@
         <f t="shared" si="2"/>
         <v>186200</v>
       </c>
-      <c r="L8" s="173">
+      <c r="L8" s="172">
         <f t="shared" si="3"/>
         <v>5727.9482400000006</v>
       </c>
@@ -3355,7 +3326,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3390,7 +3361,7 @@
         <f t="shared" si="2"/>
         <v>188440</v>
       </c>
-      <c r="L9" s="173">
+      <c r="L9" s="172">
         <f t="shared" si="3"/>
         <v>5796.855888</v>
       </c>
@@ -3412,7 +3383,7 @@
       </c>
       <c r="R9" s="45"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3444,7 +3415,7 @@
         <f t="shared" si="2"/>
         <v>225119.99999999997</v>
       </c>
-      <c r="L10" s="173">
+      <c r="L10" s="172">
         <f t="shared" si="3"/>
         <v>6925.2186239999983</v>
       </c>
@@ -3466,7 +3437,7 @@
       </c>
       <c r="R10" s="45"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3501,7 +3472,7 @@
         <f t="shared" si="2"/>
         <v>132440</v>
       </c>
-      <c r="L11" s="173">
+      <c r="L11" s="172">
         <f t="shared" si="3"/>
         <v>4074.1646880000003</v>
       </c>
@@ -3522,7 +3493,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3557,7 +3528,7 @@
         <f t="shared" si="2"/>
         <v>158760</v>
       </c>
-      <c r="L12" s="173">
+      <c r="L12" s="172">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
@@ -3578,7 +3549,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3613,7 +3584,7 @@
         <f t="shared" si="2"/>
         <v>158760</v>
       </c>
-      <c r="L13" s="173">
+      <c r="L13" s="172">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
@@ -3637,7 +3608,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3672,7 +3643,7 @@
         <f t="shared" si="2"/>
         <v>214760</v>
       </c>
-      <c r="L14" s="173">
+      <c r="L14" s="172">
         <f t="shared" si="3"/>
         <v>6606.5207519999994</v>
       </c>
@@ -3693,7 +3664,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3728,7 +3699,7 @@
         <f t="shared" si="2"/>
         <v>137200</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="172">
         <f t="shared" si="3"/>
         <v>4220.5934400000006</v>
       </c>
@@ -3749,7 +3720,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3784,7 +3755,7 @@
         <f t="shared" si="2"/>
         <v>157640</v>
       </c>
-      <c r="L16" s="173">
+      <c r="L16" s="172">
         <f t="shared" si="3"/>
         <v>4849.375728</v>
       </c>
@@ -3805,7 +3776,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3840,7 +3811,7 @@
         <f t="shared" si="2"/>
         <v>155400</v>
       </c>
-      <c r="L17" s="173">
+      <c r="L17" s="172">
         <f t="shared" si="3"/>
         <v>4780.4680799999996</v>
       </c>
@@ -3861,7 +3832,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3895,7 +3866,7 @@
         <f t="shared" si="2"/>
         <v>309680</v>
       </c>
-      <c r="L18" s="173">
+      <c r="L18" s="172">
         <f t="shared" si="3"/>
         <v>9526.4823360000009</v>
       </c>
@@ -3916,7 +3887,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3951,7 +3922,7 @@
         <f t="shared" si="2"/>
         <v>92400</v>
       </c>
-      <c r="L19" s="173">
+      <c r="L19" s="172">
         <f t="shared" si="3"/>
         <v>2842.4404799999993</v>
       </c>
@@ -3972,7 +3943,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4007,7 +3978,7 @@
         <f t="shared" si="2"/>
         <v>50400.000000000007</v>
       </c>
-      <c r="L20" s="173">
+      <c r="L20" s="172">
         <f t="shared" si="3"/>
         <v>1550.4220800000001</v>
       </c>
@@ -4028,7 +3999,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4063,7 +4034,7 @@
         <f t="shared" si="2"/>
         <v>90160</v>
       </c>
-      <c r="L21" s="173">
+      <c r="L21" s="172">
         <f t="shared" si="3"/>
         <v>2773.5328319999999</v>
       </c>
@@ -4085,7 +4056,7 @@
       </c>
       <c r="R21" s="44"/>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4119,7 +4090,7 @@
         <f t="shared" si="2"/>
         <v>73080</v>
       </c>
-      <c r="L22" s="173">
+      <c r="L22" s="172">
         <f t="shared" si="3"/>
         <v>2248.1120159999996</v>
       </c>
@@ -4140,7 +4111,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4175,7 +4146,7 @@
         <f t="shared" si="2"/>
         <v>119840.00000000001</v>
       </c>
-      <c r="L23" s="173">
+      <c r="L23" s="172">
         <f t="shared" si="3"/>
         <v>3686.5591680000002</v>
       </c>
@@ -4197,7 +4168,7 @@
       </c>
       <c r="R23" s="145"/>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
@@ -4218,7 +4189,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="86"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4236,7 +4207,7 @@
       <c r="O25" s="85"/>
       <c r="P25" s="45"/>
     </row>
-    <row r="26" spans="1:18" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="86"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4254,7 +4225,7 @@
       <c r="O26" s="85"/>
       <c r="P26" s="45"/>
     </row>
-    <row r="27" spans="1:18" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="87"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4272,7 +4243,7 @@
       <c r="O27" s="85"/>
       <c r="P27" s="45"/>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="66"/>
       <c r="B28" s="94"/>
       <c r="C28" s="94"/>
@@ -4290,7 +4261,7 @@
       <c r="O28" s="97"/>
       <c r="P28" s="45"/>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="98"/>
       <c r="B29" s="99"/>
       <c r="C29" s="99"/>
@@ -4343,107 +4314,100 @@
         <v>3280205.7100000004</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="203" t="str">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="193" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="203"/>
-      <c r="I32" s="203"/>
-      <c r="J32" s="203"/>
-      <c r="K32" s="203"/>
-      <c r="L32" s="203"/>
-      <c r="M32" s="203"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="203"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="203"/>
-      <c r="I33" s="203"/>
-      <c r="J33" s="203"/>
-      <c r="K33" s="203"/>
-      <c r="L33" s="203"/>
-      <c r="M33" s="203"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="203"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="203"/>
-      <c r="I34" s="203"/>
-      <c r="J34" s="203"/>
-      <c r="K34" s="203"/>
-      <c r="L34" s="203"/>
-      <c r="M34" s="203"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="203"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="203"/>
-      <c r="I35" s="203"/>
-      <c r="J35" s="203"/>
-      <c r="K35" s="203"/>
-      <c r="L35" s="203"/>
-      <c r="M35" s="203"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="203"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="203"/>
-      <c r="I36" s="203"/>
-      <c r="J36" s="203"/>
-      <c r="K36" s="203"/>
-      <c r="L36" s="203"/>
-      <c r="M36" s="203"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="203"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="203"/>
-      <c r="I37" s="203"/>
-      <c r="J37" s="203"/>
-      <c r="K37" s="203"/>
-      <c r="L37" s="203"/>
-      <c r="M37" s="203"/>
+      <c r="C32" s="193"/>
+      <c r="D32" s="193"/>
+      <c r="E32" s="193"/>
+      <c r="F32" s="193"/>
+      <c r="G32" s="193"/>
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
+      <c r="K32" s="193"/>
+      <c r="L32" s="193"/>
+      <c r="M32" s="193"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="193"/>
+      <c r="C33" s="193"/>
+      <c r="D33" s="193"/>
+      <c r="E33" s="193"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="193"/>
+      <c r="H33" s="193"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="193"/>
+      <c r="K33" s="193"/>
+      <c r="L33" s="193"/>
+      <c r="M33" s="193"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="193"/>
+      <c r="C34" s="193"/>
+      <c r="D34" s="193"/>
+      <c r="E34" s="193"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="193"/>
+      <c r="H34" s="193"/>
+      <c r="I34" s="193"/>
+      <c r="J34" s="193"/>
+      <c r="K34" s="193"/>
+      <c r="L34" s="193"/>
+      <c r="M34" s="193"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="193"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="193"/>
+      <c r="E35" s="193"/>
+      <c r="F35" s="193"/>
+      <c r="G35" s="193"/>
+      <c r="H35" s="193"/>
+      <c r="I35" s="193"/>
+      <c r="J35" s="193"/>
+      <c r="K35" s="193"/>
+      <c r="L35" s="193"/>
+      <c r="M35" s="193"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="193"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="193"/>
+      <c r="E36" s="193"/>
+      <c r="F36" s="193"/>
+      <c r="G36" s="193"/>
+      <c r="H36" s="193"/>
+      <c r="I36" s="193"/>
+      <c r="J36" s="193"/>
+      <c r="K36" s="193"/>
+      <c r="L36" s="193"/>
+      <c r="M36" s="193"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="193"/>
+      <c r="C37" s="193"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="193"/>
+      <c r="L37" s="193"/>
+      <c r="M37" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="E4:E5"/>
@@ -4453,6 +4417,13 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4462,14 +4433,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="220" t="s">
-        <v>119</v>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="192" t="s">
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
